--- a/Compititor's_Price/Celotex_Prices/Celotex_Prices_02-02-2026.xlsx
+++ b/Compititor's_Price/Celotex_Prices/Celotex_Prices_02-02-2026.xlsx
@@ -593,7 +593,7 @@
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>Price Not Found</t>
+          <t>Error: 500 Server Error: Internal Server Error for url: https://www.tradeinsulations.co.uk/product/celotex-25mm/</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
@@ -603,7 +603,7 @@
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>£10.15</t>
+          <t>£10.24</t>
         </is>
       </c>
       <c r="R2" t="inlineStr">
@@ -787,7 +787,7 @@
       </c>
       <c r="Q4" t="inlineStr">
         <is>
-          <t>£14.62</t>
+          <t>£14.77</t>
         </is>
       </c>
       <c r="R4" t="inlineStr">
@@ -879,7 +879,7 @@
       </c>
       <c r="Q5" t="inlineStr">
         <is>
-          <t>£15.31</t>
+          <t>£16.00</t>
         </is>
       </c>
       <c r="R5" t="inlineStr">
@@ -1063,7 +1063,7 @@
       </c>
       <c r="Q7" t="inlineStr">
         <is>
-          <t>£20.98</t>
+          <t>£21.90</t>
         </is>
       </c>
       <c r="R7" t="inlineStr">
@@ -1247,7 +1247,7 @@
       </c>
       <c r="Q9" t="inlineStr">
         <is>
-          <t>£24.04</t>
+          <t>£25.27</t>
         </is>
       </c>
       <c r="R9" t="inlineStr">
@@ -1431,7 +1431,7 @@
       </c>
       <c r="Q11" t="inlineStr">
         <is>
-          <t>£26.34</t>
+          <t>£26.83</t>
         </is>
       </c>
       <c r="R11" t="inlineStr">
@@ -1610,7 +1610,36 @@
       </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>£33.14</t>
+          <t xml:space="preserve">Error: Message: timeout: Timed out receiving message from renderer: 298.782
+  (Session info: chrome=144.0.7559.110)
+Stacktrace:
+Symbols not available. Dumping unresolved backtrace:
+	0x7ff625eaa535
+	0x7ff625eaa590
+	0x7ff625c510bd
+	0x7ff625c3dda9
+	0x7ff625c3da91
+	0x7ff625c3b6a7
+	0x7ff625c3bfff
+	0x7ff625c4b45a
+	0x7ff625c62387
+	0x7ff625c69a8a
+	0x7ff625c3c7c1
+	0x7ff625c620b4
+	0x7ff625cfa26f
+	0x7ff625c9cc9c
+	0x7ff625c9dbe3
+	0x7ff626187b60
+	0x7ff626181f5d
+	0x7ff6261a311a
+	0x7ff625ec60a5
+	0x7ff625ece73c
+	0x7ff625eb3844
+	0x7ff625eb39f6
+	0x7ff625e99a07
+	0x7ffe175ae8d7
+	0x7ffe1802c53c
+</t>
         </is>
       </c>
       <c r="Q13" t="inlineStr">
@@ -1682,7 +1711,7 @@
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>Price Not Found</t>
+          <t>Error: HTTPSConnectionPool(host='www.planetinsulation.co.uk', port=443): Read timed out.</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
@@ -1707,7 +1736,7 @@
       </c>
       <c r="Q14" t="inlineStr">
         <is>
-          <t>£37.82</t>
+          <t>£39.09</t>
         </is>
       </c>
       <c r="R14" t="inlineStr">
@@ -1799,7 +1828,7 @@
       </c>
       <c r="Q15" t="inlineStr">
         <is>
-          <t>£38.42</t>
+          <t>£39.69</t>
         </is>
       </c>
       <c r="R15" t="inlineStr">
@@ -1841,7 +1870,7 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>£40.93</t>
+          <t>Error: ('Connection aborted.', RemoteDisconnected('Remote end closed connection without response'))</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -1861,7 +1890,7 @@
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>£39.6</t>
+          <t>Error: HTTPSConnectionPool(host='www.insulation-online.com', port=443): Max retries exceeded with url: /product/celotex-xr4150-150mm/ (Caused by SSLError(SSLEOFError(8, '[SSL: UNEXPECTED_EOF_WHILE_READING] EOF occurred in violation of protocol (_ssl.c:1006)')))</t>
         </is>
       </c>
       <c r="L16" t="inlineStr">
@@ -1891,7 +1920,7 @@
       </c>
       <c r="Q16" t="inlineStr">
         <is>
-          <t>£39.12</t>
+          <t>£40.51</t>
         </is>
       </c>
       <c r="R16" t="inlineStr">
@@ -1953,7 +1982,7 @@
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>£634.53</t>
+          <t>Error: HTTPSConnectionPool(host='www.insulation-online.com', port=443): Max retries exceeded with url: /product/celotex-xr4165-165mm/ (Caused by SSLError(SSLEOFError(8, '[SSL: UNEXPECTED_EOF_WHILE_READING] EOF occurred in violation of protocol (_ssl.c:1006)')))</t>
         </is>
       </c>
       <c r="L17" t="inlineStr">
@@ -2075,7 +2104,7 @@
       </c>
       <c r="Q18" t="inlineStr">
         <is>
-          <t>POA</t>
+          <t>£11544.0</t>
         </is>
       </c>
       <c r="R18" t="inlineStr">
@@ -2433,7 +2462,7 @@
       </c>
       <c r="O22" t="inlineStr">
         <is>
-          <t>Price Not Found</t>
+          <t>Error: 500 Server Error: Internal Server Error for url: https://www.tradeinsulations.co.uk/product/celotex-72-5mm-insulated-plasterboard-pl4060/</t>
         </is>
       </c>
       <c r="P22" t="inlineStr">
@@ -2525,7 +2554,7 @@
       </c>
       <c r="O23" t="inlineStr">
         <is>
-          <t>Price Not Found</t>
+          <t>Error: 500 Server Error: Internal Server Error for url: https://www.tradeinsulations.co.uk/product/celotex-cw4050-50mm-cavity-wall-board/</t>
         </is>
       </c>
       <c r="P23" t="inlineStr">
@@ -2597,7 +2626,7 @@
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>£39.38</t>
+          <t>Error: HTTPSConnectionPool(host='www.insulation-online.com', port=443): Read timed out.</t>
         </is>
       </c>
       <c r="L24" t="inlineStr">
@@ -2617,7 +2646,7 @@
       </c>
       <c r="O24" t="inlineStr">
         <is>
-          <t>Price Not Found</t>
+          <t>Error: 500 Server Error: Internal Server Error for url: https://www.tradeinsulations.co.uk/product/celotex-cw4075-75mm-cavity-wall-board/</t>
         </is>
       </c>
       <c r="P24" t="inlineStr">
@@ -2781,7 +2810,7 @@
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>£40.53</t>
+          <t>Error: HTTPSConnectionPool(host='www.insulation-online.com', port=443): Max retries exceeded with url: /product/celotex-cw4100-100mm/ (Caused by SSLError(SSLEOFError(8, '[SSL: UNEXPECTED_EOF_WHILE_READING] EOF occurred in violation of protocol (_ssl.c:1006)')))</t>
         </is>
       </c>
       <c r="L26" t="inlineStr">
@@ -3077,7 +3106,7 @@
       </c>
       <c r="O29" t="inlineStr">
         <is>
-          <t>Price Not Found</t>
+          <t>Error: 500 Server Error: Internal Server Error for url: https://www.tradeinsulations.co.uk/product/140mm-celotex-thermaclass/</t>
         </is>
       </c>
       <c r="P29" t="inlineStr">
